--- a/Data/Input/CandidateEmailList.xlsx
+++ b/Data/Input/CandidateEmailList.xlsx
@@ -1,148 +1,127 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:workbookProtection/>
-  <x:bookViews>
-    <x:workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-  </x:sheets>
-  <x:definedNames/>
-  <x:calcPr calcId="124519" fullCalcOnLoad="1"/>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UiPath\Performer_JP\Data\Input\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32AC869-CB74-4FF9-B6F0-905D163D000F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="4548" yWindow="1452" windowWidth="17280" windowHeight="10656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="0"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t>Duong Thanh Thanh Duy</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duongduy12318@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Steve</x:t>
-  </x:si>
-</x:sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+  <si>
+    <t>duongduy12318@gmail.com</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Duong Duy</t>
+  </si>
+  <si>
+    <t>duongduy12317@gmail.com</t>
+  </si>
+  <si>
+    <t>quocuonguyen12345@gmail.com</t>
+  </si>
+  <si>
+    <t>Cu Cuong</t>
+  </si>
+  <si>
+    <t>lehuudai611@gmail.com</t>
+  </si>
+  <si>
+    <t>khang17122005@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>kinhbui2003@gmail.com</t>
+  </si>
+  <si>
+    <t>Kinh bui</t>
+  </si>
+  <si>
+    <t>Khang</t>
+  </si>
+  <si>
+    <t>Huu Dai</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="0"/>
-  <x:fonts count="2">
-    <x:font>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-      <x:color theme="1"/>
-      <x:sz val="11"/>
-      <x:scheme val="minor"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="11"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="2">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-  </x:fills>
-  <x:borders count="1">
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-      <x:diagonal/>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
-  </x:cellStyles>
-  <x:tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <x:colors>
-    <x:indexedColors>
-      <x:rgbColor rgb="00000000"/>
-      <x:rgbColor rgb="00FFFFFF"/>
-      <x:rgbColor rgb="00FF0000"/>
-      <x:rgbColor rgb="0000FF00"/>
-      <x:rgbColor rgb="000000FF"/>
-      <x:rgbColor rgb="00FFFF00"/>
-      <x:rgbColor rgb="00FF00FF"/>
-      <x:rgbColor rgb="0000FFFF"/>
-      <x:rgbColor rgb="00000000"/>
-      <x:rgbColor rgb="00FFFFFF"/>
-      <x:rgbColor rgb="00FF0000"/>
-      <x:rgbColor rgb="0000FF00"/>
-      <x:rgbColor rgb="000000FF"/>
-      <x:rgbColor rgb="00FFFF00"/>
-      <x:rgbColor rgb="00FF00FF"/>
-      <x:rgbColor rgb="0000FFFF"/>
-      <x:rgbColor rgb="00800000"/>
-      <x:rgbColor rgb="00008000"/>
-      <x:rgbColor rgb="00000080"/>
-      <x:rgbColor rgb="00808000"/>
-      <x:rgbColor rgb="00800080"/>
-      <x:rgbColor rgb="00008080"/>
-      <x:rgbColor rgb="00C0C0C0"/>
-      <x:rgbColor rgb="00808080"/>
-      <x:rgbColor rgb="009999FF"/>
-      <x:rgbColor rgb="00993366"/>
-      <x:rgbColor rgb="00FFFFCC"/>
-      <x:rgbColor rgb="00CCFFFF"/>
-      <x:rgbColor rgb="00660066"/>
-      <x:rgbColor rgb="00FF8080"/>
-      <x:rgbColor rgb="000066CC"/>
-      <x:rgbColor rgb="00CCCCFF"/>
-      <x:rgbColor rgb="00000080"/>
-      <x:rgbColor rgb="00FF00FF"/>
-      <x:rgbColor rgb="00FFFF00"/>
-      <x:rgbColor rgb="0000FFFF"/>
-      <x:rgbColor rgb="00800080"/>
-      <x:rgbColor rgb="00800000"/>
-      <x:rgbColor rgb="00008080"/>
-      <x:rgbColor rgb="000000FF"/>
-      <x:rgbColor rgb="0000CCFF"/>
-      <x:rgbColor rgb="00CCFFFF"/>
-      <x:rgbColor rgb="00CCFFCC"/>
-      <x:rgbColor rgb="00FFFF99"/>
-      <x:rgbColor rgb="0099CCFF"/>
-      <x:rgbColor rgb="00FF99CC"/>
-      <x:rgbColor rgb="00CC99FF"/>
-      <x:rgbColor rgb="00FFCC99"/>
-      <x:rgbColor rgb="003366FF"/>
-      <x:rgbColor rgb="0033CCCC"/>
-      <x:rgbColor rgb="0099CC00"/>
-      <x:rgbColor rgb="00FFCC00"/>
-      <x:rgbColor rgb="00FF9900"/>
-      <x:rgbColor rgb="00FF6600"/>
-      <x:rgbColor rgb="00666699"/>
-      <x:rgbColor rgb="00969696"/>
-      <x:rgbColor rgb="00003366"/>
-      <x:rgbColor rgb="00339966"/>
-      <x:rgbColor rgb="00003300"/>
-      <x:rgbColor rgb="00333300"/>
-      <x:rgbColor rgb="00993300"/>
-      <x:rgbColor rgb="00993366"/>
-      <x:rgbColor rgb="00333399"/>
-      <x:rgbColor rgb="00333333"/>
-    </x:indexedColors>
-  </x:colors>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+  </cellXfs>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -429,67 +408,78 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-    <x:pageSetUpPr/>
-  </x:sheetPr>
-  <x:dimension ref="A1:B2"/>
-  <x:sheetFormatPr baseColWidth="8" defaultColWidth="9.139196" defaultRowHeight="15"/>
-  <x:sheetData>
-    <x:row r="1" spans="1:2">
-      <x:c r="A1" s="0" t="inlineStr">
-        <x:is>
-          <x:t>Name</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" s="0" t="inlineStr">
-        <x:is>
-          <x:t>Email</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:2">
-      <x:c r="A2" s="0" t="inlineStr">
-        <x:is>
-          <x:t>Duong Duy</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="0" t="inlineStr">
-        <x:is>
-          <x:t>duongduy12318@gmail.com</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:2">
-      <x:c r="A3" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:2">
-      <x:c r="A4" s="0" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:2">
-      <x:c r="A5" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{4A482750-4E1E-420E-9CFB-98F22143ED8C}"/>
+    <hyperlink ref="B4" r:id="rId2" xr:uid="{21A0F0CF-ED12-46B3-B4E6-F2F8750CE425}"/>
+    <hyperlink ref="B5" r:id="rId3" xr:uid="{D7812FAA-17F7-472A-B42F-952D0087EE81}"/>
+    <hyperlink ref="B6" r:id="rId4" xr:uid="{1CC28B75-6D6D-40D1-A359-5D69916786C1}"/>
+    <hyperlink ref="B7" r:id="rId5" xr:uid="{7F031977-68E6-4A4E-9C1F-FE07CD537A23}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>